--- a/division_rank.xlsx
+++ b/division_rank.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="516">
   <si>
     <t>랭킹</t>
   </si>
@@ -1572,111 +1572,6 @@
   </si>
   <si>
     <t>WATS</t>
-  </si>
-  <si>
-    <t>A-JAX</t>
-  </si>
-  <si>
-    <t>CLEANSHOT BASKETBALL CLUB</t>
-  </si>
-  <si>
-    <t>CROSS</t>
-  </si>
-  <si>
-    <t>GP</t>
-  </si>
-  <si>
-    <t>JDBC</t>
-  </si>
-  <si>
-    <t>MERCURY(머큐리)</t>
-  </si>
-  <si>
-    <t>NTY</t>
-  </si>
-  <si>
-    <t>RDS</t>
-  </si>
-  <si>
-    <t>WOO</t>
-  </si>
-  <si>
-    <t>공주대학교ABC</t>
-  </si>
-  <si>
-    <t>광주BROS</t>
-  </si>
-  <si>
-    <t>광주낭만</t>
-  </si>
-  <si>
-    <t>광주아레스</t>
-  </si>
-  <si>
-    <t>나눔</t>
-  </si>
-  <si>
-    <t>노마드</t>
-  </si>
-  <si>
-    <t>대전피버</t>
-  </si>
-  <si>
-    <t>드림쉐이크</t>
-  </si>
-  <si>
-    <t>루키</t>
-  </si>
-  <si>
-    <t>맨투맨</t>
-  </si>
-  <si>
-    <t>목포가온</t>
-  </si>
-  <si>
-    <t>볼케이노 OB</t>
-  </si>
-  <si>
-    <t>부산DDD</t>
-  </si>
-  <si>
-    <t>삼진산업</t>
-  </si>
-  <si>
-    <t>수영구스포츠클럽</t>
-  </si>
-  <si>
-    <t>시그널</t>
-  </si>
-  <si>
-    <t>시밀러</t>
-  </si>
-  <si>
-    <t>원주엔드라인</t>
-  </si>
-  <si>
-    <t>의정부시대표</t>
-  </si>
-  <si>
-    <t>춘천라온</t>
-  </si>
-  <si>
-    <t>춘천레전드</t>
-  </si>
-  <si>
-    <t>퀀텀점프</t>
-  </si>
-  <si>
-    <t>하피이글</t>
-  </si>
-  <si>
-    <t>할스바나</t>
-  </si>
-  <si>
-    <t>화성HS</t>
-  </si>
-  <si>
-    <t>흙(CLAY)</t>
   </si>
 </sst>
 </file>
@@ -1969,7 +1864,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F1000"/>
+  <dimension ref="A1:F965"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
@@ -11779,392 +11674,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B493" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C493" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D493" s="2" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="494" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B494" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C494" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D494" s="2" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="495" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B495" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C495" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D495" s="2" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="496" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B496" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C496" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D496" s="2" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="497" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B497" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C497" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D497" s="2" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="498" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B498" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C498" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D498" s="2" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="499" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B499" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C499" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D499" s="2" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="500" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B500" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C500" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D500" s="2" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="501" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B501" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C501" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D501" s="2" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="502" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B502" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C502" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D502" s="2" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="503" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B503" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C503" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D503" s="2" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="504" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B504" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C504" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D504" s="2" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="505" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B505" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C505" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D505" s="2" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="506" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B506" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C506" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D506" s="2" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="507" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B507" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C507" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D507" s="2" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="508" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B508" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C508" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D508" s="2" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="509" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B509" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C509" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D509" s="2" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="510" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B510" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C510" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D510" s="2" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="511" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B511" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C511" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D511" s="2" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="512" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B512" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C512" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D512" s="2" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="513" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B513" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C513" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D513" s="2" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="514" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B514" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C514" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D514" s="2" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="515" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B515" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C515" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D515" s="2" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="516" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B516" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C516" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D516" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="517" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B517" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C517" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D517" s="2" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="518" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B518" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C518" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D518" s="2" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="519" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B519" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C519" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D519" s="2" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="520" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B520" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C520" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D520" s="2" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="521" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B521" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C521" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D521" s="2" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="522" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B522" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C522" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D522" s="2" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="523" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B523" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C523" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D523" s="2" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="524" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B524" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C524" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D524" s="2" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="525" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B525" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C525" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D525" s="2" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="526" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B526" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C526" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D526" s="2" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="527" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B527" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C527" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D527" s="2" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="528" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -12602,41 +12147,6 @@
     <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
